--- a/Data Files/Backoffce/EnvioRetornoGo/EnvioRetornoGo.xlsx
+++ b/Data Files/Backoffce/EnvioRetornoGo/EnvioRetornoGo.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\EnvioRetornoGo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{A2CDA133-B72E-4C2E-90AD-DC5DBA5D4E8F}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBD542E-5AA1-4844-9D49-E67883A05EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RetornoGo" r:id="rId1" sheetId="2"/>
+    <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">RetornoGo!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RetornoGo!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,13 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="55">
-  <si>
-    <t>ERRO</t>
-  </si>
-  <si>
-    <t>linha</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
   <si>
     <t xml:space="preserve">Status </t>
   </si>
@@ -65,153 +59,122 @@
     <t>Processar</t>
   </si>
   <si>
+    <t xml:space="preserve">MSG ENVIO </t>
+  </si>
+  <si>
+    <t>MSG RETORNO</t>
+  </si>
+  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>claudia.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13381647200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>gilberto.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12971897800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13391191300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>william.bonifacio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13168593100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>afonso.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13043506000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>itamar.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13384596600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>ana.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13375999000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13378926200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13378952800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13376289200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>diego.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13377281300000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13378915700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>renata.scarpino@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12581108100000 Nota 418 - Vida - Faturamento - Proposta/DPS</t>
-  </si>
-  <si>
-    <t>barbara.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13098378100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>natalia.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13335057700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12834767900000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : claudia.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : gilberto.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : william.bonifacio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : afonso.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : itamar.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : ana.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : diego.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : renata.scarpino@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : barbara.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : natalia.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Envio de e-mail retorno GO enviado para : carlos.neves@allianz.com.br</t>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13317188300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>ana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13568085200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13522631100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fernando.duque@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13087209100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fabio.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13580623800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13583112300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>daniela.gui@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13580381700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13573079400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>leandro.gonzaga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13567250500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>clarissa.cavalli@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13580626600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13546439700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>ana.guanais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-30108972860 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fabio.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13576780800000 Nota 595 - ERRO PDF alteração</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13578210200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>deise.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13580542900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13582911200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13578615400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>nicole.demori@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13584652200000 Nota 595 - ERRO PDF retorno</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +186,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -243,13 +214,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,21 +234,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -294,10 +268,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -332,7 +306,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -384,7 +358,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -495,21 +469,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -526,7 +500,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -578,405 +552,344 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="42.42578125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="4" width="80.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="183.0" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="16.42578125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="84.28515625" collapsed="true"/>
+    <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="80" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="183" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="84.28515625" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="84.28515625" style="3" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
+      <c r="E1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="4">
-        <v>3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="4">
-        <v>4</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="4">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="4">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="4">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="4">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="B11" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="4">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="4">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="4">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="C14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="4">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="4">
-        <v>13</v>
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="E16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="4">
-        <v>15</v>
+      <c r="B18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECF9874-EDD0-4B43-8017-C343DACF060B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/EnvioRetornoGo/EnvioRetornoGo.xlsx
+++ b/Data Files/Backoffce/EnvioRetornoGo/EnvioRetornoGo.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\EnvioRetornoGo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBD542E-5AA1-4844-9D49-E67883A05EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{B88D0AD1-7377-4999-AD86-AC5EACFE6360}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="RetornoGo" sheetId="2" r:id="rId1"/>
+    <sheet name="RetornoGo" r:id="rId1" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RetornoGo!$A$1:$E$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">RetornoGo!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t xml:space="preserve">Status </t>
   </si>
@@ -53,9 +53,6 @@
     <t>Corpo do e-mail</t>
   </si>
   <si>
-    <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
-  </si>
-  <si>
     <t>Processar</t>
   </si>
   <si>
@@ -65,115 +62,29 @@
     <t>MSG RETORNO</t>
   </si>
   <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13317188300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>ana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13568085200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13522631100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>fernando.duque@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13087209100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fabio.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580623800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>priscila.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13583112300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>daniela.gui@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580381700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>raphael.callado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13573079400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>leandro.gonzaga@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13567250500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>clarissa.cavalli@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580626600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>viviane.corbari@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13546439700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>ana.guanais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-30108972860 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fabio.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13576780800000 Nota 595 - ERRO PDF alteração</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13578210200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>deise.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13580542900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13582911200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>eduardo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13578615400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>nicole.demori@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13584652200000 Nota 595 - ERRO PDF retorno</t>
+    <t>Prezado(a), existe uma tarefa no GO pendente de análise.Por favor, acesse seu painel para validação e retorno.Este e-mail é um envio automático, favor não responder. Att.</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO Referência: 14103343000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>Envio de e-mail retorno GO enviado</t>
+  </si>
+  <si>
+    <t>Envio de e-mail retorno GO enviado para : cristiane.lozano@allianz.com.br</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -235,23 +146,22 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  <cellXfs count="5">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="1"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="8" name="Hiperlink" xfId="1"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -268,10 +178,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -306,7 +216,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -358,7 +268,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -469,21 +379,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -500,7 +410,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -552,26 +462,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.42578125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="80" style="3" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="183" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="84.28515625" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="84.28515625" style="3" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="42.42578125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="80.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="183.0" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="16.42578125" collapsed="true"/>
+    <col min="5" max="6" customWidth="true" width="84.28515625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,279 +496,44 @@
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>6</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2"/>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="A3" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>
